--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S464"/>
+  <dimension ref="A1:S465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24247,6 +24247,59 @@
         <v>10</v>
       </c>
       <c r="S464" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>462</v>
+      </c>
+      <c r="B465" t="inlineStr"/>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>MT약품</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>MT약품</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="n">
+        <v>0</v>
+      </c>
+      <c r="L465" t="n">
+        <v>0</v>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr"/>
+      <c r="O465" t="inlineStr"/>
+      <c r="P465" t="inlineStr"/>
+      <c r="Q465" t="n">
+        <v>0</v>
+      </c>
+      <c r="R465" t="n">
+        <v>10</v>
+      </c>
+      <c r="S465" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24261,7 +24314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24411,10 +24464,26 @@
           <t>K1-PJT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -24427,6 +24496,273 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B3" t="n">
+        <v>405</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K1-PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B4" t="n">
+        <v>408</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>K1-PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45778.88671622195</v>
+      </c>
+      <c r="B5" t="n">
+        <v>433</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>K1-PJT 현장 사용 (자동 차감) (nan)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45778.88671622195</v>
+      </c>
+      <c r="B6" t="n">
+        <v>434</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>K1-PJT 현장 사용 (자동 차감) (nan)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B7" t="n">
+        <v>462</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>K1-PJT 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24500,7 +24836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24906,7 +25242,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -24920,13 +25256,9 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" s="1" t="n">
-        <v>46147.34000990329</v>
+        <v>46147.34000990741</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -24994,66 +25326,48 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AA2" t="n">
+        <v>0</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AD2" t="n">
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AG2" t="n">
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AJ2" t="n">
+        <v>0</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP2" t="n">
+        <v>0</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AS2" t="n">
+        <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AV2" t="n">
+        <v>0</v>
       </c>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY2" t="n">
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -25096,11 +25410,7 @@
       <c r="BL2" t="n">
         <v>2</v>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr">
         <is>
           <t>롯데건설</t>
@@ -25123,11 +25433,7 @@
           <t>ASME B31.3</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -25135,7 +25441,625 @@
         </is>
       </c>
       <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr"/>
+      <c r="CB2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>405</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="1" t="n">
+        <v>46147.87794667824</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>408</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="1" t="n">
+        <v>46147.87911841435</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>25500</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>K1-PJT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>462</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>46147.88671621533</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4300</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>86000</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>스타렉스91주8839</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>롯데건설</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>ASME B31.3</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -21,11 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -56,10 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S465"/>
+  <dimension ref="A1:S455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,7 +569,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -625,7 +622,7 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -678,7 +675,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -731,7 +728,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -784,7 +781,7 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -837,7 +834,7 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -890,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -943,7 +940,7 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -996,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1049,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1102,7 +1099,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1155,7 +1152,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1208,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1261,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1314,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1367,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1420,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1473,7 +1470,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1526,7 +1523,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1579,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -1632,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -1685,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -1738,7 +1735,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -1791,7 +1788,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -1844,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -1897,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -1950,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2003,7 +2000,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2056,7 +2053,7 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2109,7 +2106,7 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -2162,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -2215,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -2268,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -2321,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -2374,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -2427,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -2480,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -2533,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -2586,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -2639,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -2692,7 +2689,7 @@
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -2745,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -2798,7 +2795,7 @@
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -2851,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -2904,7 +2901,7 @@
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -2957,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -3006,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -3055,7 +3052,7 @@
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -3104,7 +3101,7 @@
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -3153,7 +3150,7 @@
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -3202,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -3255,7 +3252,7 @@
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -3308,7 +3305,7 @@
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -3361,7 +3358,7 @@
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -3414,7 +3411,7 @@
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -3467,7 +3464,7 @@
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -3520,7 +3517,7 @@
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -3573,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -3626,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -3679,7 +3676,7 @@
         <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -3732,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -3785,7 +3782,7 @@
         <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -3838,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -3891,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -3944,7 +3941,7 @@
         <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -3993,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -4042,7 +4039,7 @@
         <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -4095,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -4148,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -4201,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -4254,7 +4251,7 @@
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -4307,7 +4304,7 @@
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -4360,7 +4357,7 @@
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -4413,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -4466,7 +4463,7 @@
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -4519,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -4572,7 +4569,7 @@
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -4625,7 +4622,7 @@
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -4678,7 +4675,7 @@
         <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -4731,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -4784,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -4837,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -4890,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -4943,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -4996,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -5049,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -5102,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -5155,7 +5152,7 @@
         <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -5208,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -5261,7 +5258,7 @@
         <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -5314,7 +5311,7 @@
         <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -5367,7 +5364,7 @@
         <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -5416,7 +5413,7 @@
         <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -5469,7 +5466,7 @@
         <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -5522,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -5575,7 +5572,7 @@
         <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -5628,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -5681,7 +5678,7 @@
         <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -5734,7 +5731,7 @@
         <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -5787,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -5840,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -5893,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -5946,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -5999,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -6052,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -6101,7 +6098,7 @@
         <v>1</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -6150,7 +6147,7 @@
         <v>2</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -6199,7 +6196,7 @@
         <v>10</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -6248,7 +6245,7 @@
         <v>10</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -6297,7 +6294,7 @@
         <v>10</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -6346,7 +6343,7 @@
         <v>10</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -6395,7 +6392,7 @@
         <v>10</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -6444,7 +6441,7 @@
         <v>10</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -6493,7 +6490,7 @@
         <v>10</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -6542,7 +6539,7 @@
         <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -6591,7 +6588,7 @@
         <v>2</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -6640,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -6689,7 +6686,7 @@
         <v>1</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -6738,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -6787,7 +6784,7 @@
         <v>1</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -6836,7 +6833,7 @@
         <v>1</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -6885,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -6934,7 +6931,7 @@
         <v>53</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -6983,7 +6980,7 @@
         <v>76</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -7032,7 +7029,7 @@
         <v>50</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -7081,7 +7078,7 @@
         <v>13</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -7130,7 +7127,7 @@
         <v>8</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -7179,7 +7176,7 @@
         <v>14</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -7228,7 +7225,7 @@
         <v>16</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -7277,7 +7274,7 @@
         <v>2</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -7326,7 +7323,7 @@
         <v>10</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -7375,7 +7372,7 @@
         <v>8</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -7424,7 +7421,7 @@
         <v>11</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -7473,7 +7470,7 @@
         <v>12</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -7522,7 +7519,7 @@
         <v>14</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -7571,7 +7568,7 @@
         <v>10</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -7620,7 +7617,7 @@
         <v>9</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -7669,7 +7666,7 @@
         <v>6</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -7718,7 +7715,7 @@
         <v>19</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -7767,7 +7764,7 @@
         <v>2</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -7816,7 +7813,7 @@
         <v>4</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -7865,7 +7862,7 @@
         <v>21</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -7914,7 +7911,7 @@
         <v>34</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -7963,7 +7960,7 @@
         <v>10</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -8012,7 +8009,7 @@
         <v>2</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -8061,7 +8058,7 @@
         <v>2</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -8110,7 +8107,7 @@
         <v>3</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -8159,7 +8156,7 @@
         <v>2</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -8208,7 +8205,7 @@
         <v>2</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -8257,7 +8254,7 @@
         <v>4</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -8306,7 +8303,7 @@
         <v>13</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -8355,7 +8352,7 @@
         <v>16</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -8404,7 +8401,7 @@
         <v>26</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S154" t="n">
         <v>0</v>
@@ -8453,7 +8450,7 @@
         <v>4</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -8502,7 +8499,7 @@
         <v>5</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -8551,7 +8548,7 @@
         <v>50</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -8600,7 +8597,7 @@
         <v>34</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -8649,7 +8646,7 @@
         <v>92</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -8698,7 +8695,7 @@
         <v>168</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -8747,7 +8744,7 @@
         <v>65</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -8796,7 +8793,7 @@
         <v>80</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -8845,7 +8842,7 @@
         <v>492</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S163" t="n">
         <v>0</v>
@@ -8894,7 +8891,7 @@
         <v>491</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S164" t="n">
         <v>0</v>
@@ -8943,7 +8940,7 @@
         <v>324</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -8992,7 +8989,7 @@
         <v>252</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -9041,7 +9038,7 @@
         <v>75</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -9090,7 +9087,7 @@
         <v>67</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -9139,7 +9136,7 @@
         <v>458</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -9188,7 +9185,7 @@
         <v>696</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -9237,7 +9234,7 @@
         <v>70</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -9286,7 +9283,7 @@
         <v>522</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -9335,7 +9332,7 @@
         <v>22</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -9384,7 +9381,7 @@
         <v>5</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -9437,7 +9434,7 @@
         <v>1</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -9490,7 +9487,7 @@
         <v>1</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S176" t="n">
         <v>0</v>
@@ -9539,7 +9536,7 @@
         <v>1</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S177" t="n">
         <v>0</v>
@@ -9588,7 +9585,7 @@
         <v>3</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
@@ -9637,7 +9634,7 @@
         <v>2</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
@@ -9686,7 +9683,7 @@
         <v>2</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S180" t="n">
         <v>0</v>
@@ -9735,7 +9732,7 @@
         <v>2</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S181" t="n">
         <v>0</v>
@@ -9784,7 +9781,7 @@
         <v>2</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -9833,7 +9830,7 @@
         <v>2</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -9882,7 +9879,7 @@
         <v>1</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -9931,7 +9928,7 @@
         <v>2</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -9980,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -10029,7 +10026,7 @@
         <v>1</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -10078,7 +10075,7 @@
         <v>1</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -10127,7 +10124,7 @@
         <v>1</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -10176,7 +10173,7 @@
         <v>1</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S190" t="n">
         <v>0</v>
@@ -10225,7 +10222,7 @@
         <v>1</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -10274,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -10323,7 +10320,7 @@
         <v>1</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -10372,7 +10369,7 @@
         <v>1</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -10421,7 +10418,7 @@
         <v>1</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -10470,7 +10467,7 @@
         <v>1</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -10519,7 +10516,7 @@
         <v>1</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -10568,7 +10565,7 @@
         <v>1</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -10617,7 +10614,7 @@
         <v>1</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S199" t="n">
         <v>0</v>
@@ -10666,7 +10663,7 @@
         <v>1</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S200" t="n">
         <v>0</v>
@@ -10715,7 +10712,7 @@
         <v>1</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S201" t="n">
         <v>0</v>
@@ -10764,7 +10761,7 @@
         <v>1</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S202" t="n">
         <v>0</v>
@@ -10813,7 +10810,7 @@
         <v>1</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -10862,7 +10859,7 @@
         <v>1</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -10911,7 +10908,7 @@
         <v>1</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -10960,7 +10957,7 @@
         <v>1</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -11009,7 +11006,7 @@
         <v>1</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -11058,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -11107,7 +11104,7 @@
         <v>1</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -11160,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -11213,7 +11210,7 @@
         <v>1</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -11266,7 +11263,7 @@
         <v>1</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -11319,7 +11316,7 @@
         <v>1</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -11372,7 +11369,7 @@
         <v>1</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -11425,7 +11422,7 @@
         <v>1</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -11478,7 +11475,7 @@
         <v>1</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S216" t="n">
         <v>0</v>
@@ -11531,7 +11528,7 @@
         <v>1</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -11584,7 +11581,7 @@
         <v>1</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>
@@ -11637,7 +11634,7 @@
         <v>1</v>
       </c>
       <c r="R219" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S219" t="n">
         <v>0</v>
@@ -11690,7 +11687,7 @@
         <v>1</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -11743,7 +11740,7 @@
         <v>1</v>
       </c>
       <c r="R221" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -11796,7 +11793,7 @@
         <v>1</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S222" t="n">
         <v>0</v>
@@ -11849,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="R223" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S223" t="n">
         <v>0</v>
@@ -11902,7 +11899,7 @@
         <v>1</v>
       </c>
       <c r="R224" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S224" t="n">
         <v>0</v>
@@ -11955,7 +11952,7 @@
         <v>1</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S225" t="n">
         <v>0</v>
@@ -12008,7 +12005,7 @@
         <v>1</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
@@ -12061,7 +12058,7 @@
         <v>1</v>
       </c>
       <c r="R227" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S227" t="n">
         <v>0</v>
@@ -12114,7 +12111,7 @@
         <v>1</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S228" t="n">
         <v>0</v>
@@ -12163,7 +12160,7 @@
         <v>1</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S229" t="n">
         <v>0</v>
@@ -12216,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S230" t="n">
         <v>0</v>
@@ -12269,7 +12266,7 @@
         <v>1</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S231" t="n">
         <v>0</v>
@@ -12322,7 +12319,7 @@
         <v>1</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S232" t="n">
         <v>0</v>
@@ -12375,7 +12372,7 @@
         <v>1</v>
       </c>
       <c r="R233" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S233" t="n">
         <v>0</v>
@@ -12428,7 +12425,7 @@
         <v>1</v>
       </c>
       <c r="R234" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S234" t="n">
         <v>0</v>
@@ -12481,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="R235" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S235" t="n">
         <v>0</v>
@@ -12534,7 +12531,7 @@
         <v>1</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S236" t="n">
         <v>0</v>
@@ -12587,7 +12584,7 @@
         <v>1</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S237" t="n">
         <v>0</v>
@@ -12640,7 +12637,7 @@
         <v>1</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -12693,7 +12690,7 @@
         <v>1</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -12746,7 +12743,7 @@
         <v>1</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -12799,7 +12796,7 @@
         <v>1</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -12852,7 +12849,7 @@
         <v>1</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -12905,7 +12902,7 @@
         <v>1</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -12958,7 +12955,7 @@
         <v>5</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S244" t="n">
         <v>0</v>
@@ -13007,7 +13004,7 @@
         <v>1</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S245" t="n">
         <v>0</v>
@@ -13056,7 +13053,7 @@
         <v>1</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S246" t="n">
         <v>0</v>
@@ -13105,7 +13102,7 @@
         <v>1</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S247" t="n">
         <v>0</v>
@@ -13158,7 +13155,7 @@
         <v>2</v>
       </c>
       <c r="R248" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S248" t="n">
         <v>0</v>
@@ -13211,7 +13208,7 @@
         <v>2</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S249" t="n">
         <v>0</v>
@@ -13260,7 +13257,7 @@
         <v>4</v>
       </c>
       <c r="R250" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S250" t="n">
         <v>0</v>
@@ -13313,7 +13310,7 @@
         <v>1</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S251" t="n">
         <v>0</v>
@@ -13362,7 +13359,7 @@
         <v>1</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S252" t="n">
         <v>0</v>
@@ -13411,7 +13408,7 @@
         <v>3</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S253" t="n">
         <v>0</v>
@@ -13464,7 +13461,7 @@
         <v>2</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S254" t="n">
         <v>0</v>
@@ -13517,7 +13514,7 @@
         <v>1</v>
       </c>
       <c r="R255" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S255" t="n">
         <v>0</v>
@@ -13570,7 +13567,7 @@
         <v>1</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S256" t="n">
         <v>0</v>
@@ -13623,7 +13620,7 @@
         <v>1</v>
       </c>
       <c r="R257" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S257" t="n">
         <v>0</v>
@@ -13676,7 +13673,7 @@
         <v>2</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S258" t="n">
         <v>0</v>
@@ -13729,7 +13726,7 @@
         <v>1</v>
       </c>
       <c r="R259" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S259" t="n">
         <v>0</v>
@@ -13782,7 +13779,7 @@
         <v>1</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S260" t="n">
         <v>0</v>
@@ -13831,7 +13828,7 @@
         <v>1</v>
       </c>
       <c r="R261" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S261" t="n">
         <v>0</v>
@@ -13884,7 +13881,7 @@
         <v>1</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S262" t="n">
         <v>0</v>
@@ -13937,7 +13934,7 @@
         <v>1</v>
       </c>
       <c r="R263" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S263" t="n">
         <v>0</v>
@@ -13990,7 +13987,7 @@
         <v>1</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S264" t="n">
         <v>0</v>
@@ -14043,7 +14040,7 @@
         <v>1</v>
       </c>
       <c r="R265" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S265" t="n">
         <v>0</v>
@@ -14096,7 +14093,7 @@
         <v>1</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S266" t="n">
         <v>0</v>
@@ -14149,7 +14146,7 @@
         <v>1</v>
       </c>
       <c r="R267" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S267" t="n">
         <v>0</v>
@@ -14202,7 +14199,7 @@
         <v>1</v>
       </c>
       <c r="R268" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S268" t="n">
         <v>0</v>
@@ -14255,7 +14252,7 @@
         <v>1</v>
       </c>
       <c r="R269" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S269" t="n">
         <v>0</v>
@@ -14308,7 +14305,7 @@
         <v>1</v>
       </c>
       <c r="R270" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S270" t="n">
         <v>0</v>
@@ -14361,7 +14358,7 @@
         <v>1</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S271" t="n">
         <v>0</v>
@@ -14414,7 +14411,7 @@
         <v>1</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S272" t="n">
         <v>0</v>
@@ -14467,7 +14464,7 @@
         <v>1</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S273" t="n">
         <v>0</v>
@@ -14520,7 +14517,7 @@
         <v>1</v>
       </c>
       <c r="R274" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S274" t="n">
         <v>0</v>
@@ -14573,7 +14570,7 @@
         <v>1</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S275" t="n">
         <v>0</v>
@@ -14626,7 +14623,7 @@
         <v>1</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S276" t="n">
         <v>0</v>
@@ -14679,7 +14676,7 @@
         <v>1</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S277" t="n">
         <v>0</v>
@@ -14732,7 +14729,7 @@
         <v>1</v>
       </c>
       <c r="R278" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S278" t="n">
         <v>0</v>
@@ -14785,7 +14782,7 @@
         <v>1</v>
       </c>
       <c r="R279" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S279" t="n">
         <v>0</v>
@@ -14838,7 +14835,7 @@
         <v>1</v>
       </c>
       <c r="R280" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S280" t="n">
         <v>0</v>
@@ -14891,7 +14888,7 @@
         <v>1</v>
       </c>
       <c r="R281" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -14944,7 +14941,7 @@
         <v>1</v>
       </c>
       <c r="R282" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S282" t="n">
         <v>0</v>
@@ -14997,7 +14994,7 @@
         <v>1</v>
       </c>
       <c r="R283" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S283" t="n">
         <v>0</v>
@@ -15050,7 +15047,7 @@
         <v>1</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -15103,7 +15100,7 @@
         <v>1</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S285" t="n">
         <v>0</v>
@@ -15156,7 +15153,7 @@
         <v>1</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -15209,7 +15206,7 @@
         <v>1</v>
       </c>
       <c r="R287" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S287" t="n">
         <v>0</v>
@@ -15262,7 +15259,7 @@
         <v>1</v>
       </c>
       <c r="R288" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S288" t="n">
         <v>0</v>
@@ -15315,7 +15312,7 @@
         <v>1</v>
       </c>
       <c r="R289" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S289" t="n">
         <v>0</v>
@@ -15368,7 +15365,7 @@
         <v>1</v>
       </c>
       <c r="R290" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S290" t="n">
         <v>0</v>
@@ -15421,7 +15418,7 @@
         <v>1</v>
       </c>
       <c r="R291" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S291" t="n">
         <v>0</v>
@@ -15474,7 +15471,7 @@
         <v>1</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S292" t="n">
         <v>0</v>
@@ -15527,7 +15524,7 @@
         <v>1</v>
       </c>
       <c r="R293" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S293" t="n">
         <v>0</v>
@@ -15580,7 +15577,7 @@
         <v>1</v>
       </c>
       <c r="R294" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S294" t="n">
         <v>0</v>
@@ -15633,7 +15630,7 @@
         <v>1</v>
       </c>
       <c r="R295" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S295" t="n">
         <v>0</v>
@@ -15686,7 +15683,7 @@
         <v>1</v>
       </c>
       <c r="R296" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S296" t="n">
         <v>0</v>
@@ -15739,7 +15736,7 @@
         <v>1</v>
       </c>
       <c r="R297" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S297" t="n">
         <v>0</v>
@@ -15792,7 +15789,7 @@
         <v>1</v>
       </c>
       <c r="R298" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S298" t="n">
         <v>0</v>
@@ -15845,7 +15842,7 @@
         <v>1</v>
       </c>
       <c r="R299" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S299" t="n">
         <v>0</v>
@@ -15898,7 +15895,7 @@
         <v>1</v>
       </c>
       <c r="R300" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S300" t="n">
         <v>0</v>
@@ -15951,7 +15948,7 @@
         <v>1</v>
       </c>
       <c r="R301" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S301" t="n">
         <v>0</v>
@@ -16004,7 +16001,7 @@
         <v>1</v>
       </c>
       <c r="R302" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S302" t="n">
         <v>0</v>
@@ -16057,7 +16054,7 @@
         <v>1</v>
       </c>
       <c r="R303" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S303" t="n">
         <v>0</v>
@@ -16110,7 +16107,7 @@
         <v>1</v>
       </c>
       <c r="R304" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S304" t="n">
         <v>0</v>
@@ -16163,7 +16160,7 @@
         <v>1</v>
       </c>
       <c r="R305" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S305" t="n">
         <v>0</v>
@@ -16216,7 +16213,7 @@
         <v>1</v>
       </c>
       <c r="R306" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S306" t="n">
         <v>0</v>
@@ -16269,7 +16266,7 @@
         <v>1</v>
       </c>
       <c r="R307" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S307" t="n">
         <v>0</v>
@@ -16322,7 +16319,7 @@
         <v>1</v>
       </c>
       <c r="R308" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S308" t="n">
         <v>0</v>
@@ -16375,7 +16372,7 @@
         <v>1</v>
       </c>
       <c r="R309" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S309" t="n">
         <v>0</v>
@@ -16428,7 +16425,7 @@
         <v>1</v>
       </c>
       <c r="R310" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S310" t="n">
         <v>0</v>
@@ -16481,7 +16478,7 @@
         <v>1</v>
       </c>
       <c r="R311" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S311" t="n">
         <v>0</v>
@@ -16534,7 +16531,7 @@
         <v>1</v>
       </c>
       <c r="R312" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S312" t="n">
         <v>0</v>
@@ -16587,7 +16584,7 @@
         <v>1</v>
       </c>
       <c r="R313" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S313" t="n">
         <v>0</v>
@@ -16640,7 +16637,7 @@
         <v>1</v>
       </c>
       <c r="R314" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S314" t="n">
         <v>0</v>
@@ -16693,7 +16690,7 @@
         <v>1</v>
       </c>
       <c r="R315" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S315" t="n">
         <v>0</v>
@@ -16746,7 +16743,7 @@
         <v>1</v>
       </c>
       <c r="R316" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S316" t="n">
         <v>0</v>
@@ -16799,7 +16796,7 @@
         <v>1</v>
       </c>
       <c r="R317" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S317" t="n">
         <v>0</v>
@@ -16852,7 +16849,7 @@
         <v>1</v>
       </c>
       <c r="R318" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S318" t="n">
         <v>0</v>
@@ -16905,7 +16902,7 @@
         <v>1</v>
       </c>
       <c r="R319" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -16958,7 +16955,7 @@
         <v>1</v>
       </c>
       <c r="R320" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S320" t="n">
         <v>0</v>
@@ -17011,7 +17008,7 @@
         <v>1</v>
       </c>
       <c r="R321" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -17064,7 +17061,7 @@
         <v>1</v>
       </c>
       <c r="R322" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -17117,7 +17114,7 @@
         <v>1</v>
       </c>
       <c r="R323" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S323" t="n">
         <v>0</v>
@@ -17170,7 +17167,7 @@
         <v>1</v>
       </c>
       <c r="R324" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S324" t="n">
         <v>0</v>
@@ -17223,7 +17220,7 @@
         <v>1</v>
       </c>
       <c r="R325" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S325" t="n">
         <v>0</v>
@@ -17276,7 +17273,7 @@
         <v>1</v>
       </c>
       <c r="R326" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S326" t="n">
         <v>0</v>
@@ -17329,7 +17326,7 @@
         <v>1</v>
       </c>
       <c r="R327" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S327" t="n">
         <v>0</v>
@@ -17382,7 +17379,7 @@
         <v>1</v>
       </c>
       <c r="R328" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S328" t="n">
         <v>0</v>
@@ -17435,7 +17432,7 @@
         <v>1</v>
       </c>
       <c r="R329" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S329" t="n">
         <v>0</v>
@@ -17488,7 +17485,7 @@
         <v>1</v>
       </c>
       <c r="R330" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S330" t="n">
         <v>0</v>
@@ -17541,7 +17538,7 @@
         <v>1</v>
       </c>
       <c r="R331" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S331" t="n">
         <v>0</v>
@@ -17594,7 +17591,7 @@
         <v>1</v>
       </c>
       <c r="R332" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S332" t="n">
         <v>0</v>
@@ -17647,7 +17644,7 @@
         <v>1</v>
       </c>
       <c r="R333" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S333" t="n">
         <v>0</v>
@@ -17700,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="R334" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S334" t="n">
         <v>0</v>
@@ -17753,7 +17750,7 @@
         <v>1</v>
       </c>
       <c r="R335" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S335" t="n">
         <v>0</v>
@@ -17806,7 +17803,7 @@
         <v>1</v>
       </c>
       <c r="R336" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S336" t="n">
         <v>0</v>
@@ -17859,7 +17856,7 @@
         <v>1</v>
       </c>
       <c r="R337" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S337" t="n">
         <v>0</v>
@@ -17912,7 +17909,7 @@
         <v>1</v>
       </c>
       <c r="R338" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S338" t="n">
         <v>0</v>
@@ -17965,7 +17962,7 @@
         <v>1</v>
       </c>
       <c r="R339" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S339" t="n">
         <v>0</v>
@@ -18018,7 +18015,7 @@
         <v>1</v>
       </c>
       <c r="R340" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S340" t="n">
         <v>0</v>
@@ -18071,7 +18068,7 @@
         <v>1</v>
       </c>
       <c r="R341" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S341" t="n">
         <v>0</v>
@@ -18124,7 +18121,7 @@
         <v>1</v>
       </c>
       <c r="R342" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S342" t="n">
         <v>0</v>
@@ -18177,7 +18174,7 @@
         <v>1</v>
       </c>
       <c r="R343" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S343" t="n">
         <v>0</v>
@@ -18230,7 +18227,7 @@
         <v>1</v>
       </c>
       <c r="R344" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S344" t="n">
         <v>0</v>
@@ -18283,7 +18280,7 @@
         <v>1</v>
       </c>
       <c r="R345" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S345" t="n">
         <v>0</v>
@@ -18336,7 +18333,7 @@
         <v>1</v>
       </c>
       <c r="R346" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S346" t="n">
         <v>0</v>
@@ -18389,7 +18386,7 @@
         <v>1</v>
       </c>
       <c r="R347" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S347" t="n">
         <v>0</v>
@@ -18442,7 +18439,7 @@
         <v>1</v>
       </c>
       <c r="R348" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S348" t="n">
         <v>0</v>
@@ -18495,7 +18492,7 @@
         <v>1</v>
       </c>
       <c r="R349" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S349" t="n">
         <v>0</v>
@@ -18548,7 +18545,7 @@
         <v>1</v>
       </c>
       <c r="R350" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S350" t="n">
         <v>0</v>
@@ -18601,7 +18598,7 @@
         <v>1</v>
       </c>
       <c r="R351" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S351" t="n">
         <v>0</v>
@@ -18654,7 +18651,7 @@
         <v>1</v>
       </c>
       <c r="R352" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S352" t="n">
         <v>0</v>
@@ -18707,7 +18704,7 @@
         <v>1</v>
       </c>
       <c r="R353" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S353" t="n">
         <v>0</v>
@@ -18760,7 +18757,7 @@
         <v>1</v>
       </c>
       <c r="R354" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S354" t="n">
         <v>0</v>
@@ -18813,7 +18810,7 @@
         <v>1</v>
       </c>
       <c r="R355" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S355" t="n">
         <v>0</v>
@@ -18866,7 +18863,7 @@
         <v>1</v>
       </c>
       <c r="R356" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S356" t="n">
         <v>0</v>
@@ -18915,7 +18912,7 @@
         <v>1</v>
       </c>
       <c r="R357" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S357" t="n">
         <v>0</v>
@@ -18968,7 +18965,7 @@
         <v>1</v>
       </c>
       <c r="R358" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S358" t="n">
         <v>0</v>
@@ -19017,7 +19014,7 @@
         <v>1</v>
       </c>
       <c r="R359" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S359" t="n">
         <v>0</v>
@@ -19066,7 +19063,7 @@
         <v>1</v>
       </c>
       <c r="R360" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S360" t="n">
         <v>0</v>
@@ -19115,7 +19112,7 @@
         <v>1</v>
       </c>
       <c r="R361" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S361" t="n">
         <v>0</v>
@@ -19164,7 +19161,7 @@
         <v>1</v>
       </c>
       <c r="R362" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S362" t="n">
         <v>0</v>
@@ -19213,7 +19210,7 @@
         <v>1</v>
       </c>
       <c r="R363" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S363" t="n">
         <v>0</v>
@@ -19262,7 +19259,7 @@
         <v>1</v>
       </c>
       <c r="R364" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S364" t="n">
         <v>0</v>
@@ -19311,7 +19308,7 @@
         <v>1</v>
       </c>
       <c r="R365" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S365" t="n">
         <v>0</v>
@@ -19360,7 +19357,7 @@
         <v>1</v>
       </c>
       <c r="R366" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S366" t="n">
         <v>0</v>
@@ -19409,7 +19406,7 @@
         <v>1</v>
       </c>
       <c r="R367" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S367" t="n">
         <v>0</v>
@@ -19458,7 +19455,7 @@
         <v>1</v>
       </c>
       <c r="R368" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S368" t="n">
         <v>0</v>
@@ -19507,7 +19504,7 @@
         <v>2</v>
       </c>
       <c r="R369" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S369" t="n">
         <v>0</v>
@@ -19556,7 +19553,7 @@
         <v>1</v>
       </c>
       <c r="R370" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S370" t="n">
         <v>0</v>
@@ -19605,7 +19602,7 @@
         <v>1</v>
       </c>
       <c r="R371" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S371" t="n">
         <v>0</v>
@@ -19654,7 +19651,7 @@
         <v>1</v>
       </c>
       <c r="R372" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S372" t="n">
         <v>0</v>
@@ -19703,7 +19700,7 @@
         <v>1</v>
       </c>
       <c r="R373" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S373" t="n">
         <v>0</v>
@@ -19752,7 +19749,7 @@
         <v>1</v>
       </c>
       <c r="R374" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S374" t="n">
         <v>0</v>
@@ -19801,7 +19798,7 @@
         <v>1</v>
       </c>
       <c r="R375" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S375" t="n">
         <v>0</v>
@@ -19854,7 +19851,7 @@
         <v>1</v>
       </c>
       <c r="R376" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S376" t="n">
         <v>0</v>
@@ -19907,7 +19904,7 @@
         <v>1</v>
       </c>
       <c r="R377" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S377" t="n">
         <v>0</v>
@@ -19956,7 +19953,7 @@
         <v>1</v>
       </c>
       <c r="R378" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S378" t="n">
         <v>0</v>
@@ -20005,7 +20002,7 @@
         <v>1</v>
       </c>
       <c r="R379" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S379" t="n">
         <v>0</v>
@@ -20054,7 +20051,7 @@
         <v>1</v>
       </c>
       <c r="R380" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S380" t="n">
         <v>0</v>
@@ -20107,7 +20104,7 @@
         <v>1</v>
       </c>
       <c r="R381" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S381" t="n">
         <v>0</v>
@@ -20160,7 +20157,7 @@
         <v>1</v>
       </c>
       <c r="R382" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S382" t="n">
         <v>0</v>
@@ -20213,7 +20210,7 @@
         <v>1</v>
       </c>
       <c r="R383" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S383" t="n">
         <v>0</v>
@@ -20266,7 +20263,7 @@
         <v>1</v>
       </c>
       <c r="R384" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S384" t="n">
         <v>0</v>
@@ -20319,7 +20316,7 @@
         <v>1</v>
       </c>
       <c r="R385" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S385" t="n">
         <v>0</v>
@@ -20372,7 +20369,7 @@
         <v>1</v>
       </c>
       <c r="R386" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S386" t="n">
         <v>0</v>
@@ -20425,7 +20422,7 @@
         <v>1</v>
       </c>
       <c r="R387" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S387" t="n">
         <v>0</v>
@@ -20474,7 +20471,7 @@
         <v>1</v>
       </c>
       <c r="R388" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S388" t="n">
         <v>0</v>
@@ -20527,7 +20524,7 @@
         <v>1</v>
       </c>
       <c r="R389" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S389" t="n">
         <v>0</v>
@@ -20580,7 +20577,7 @@
         <v>1</v>
       </c>
       <c r="R390" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S390" t="n">
         <v>0</v>
@@ -20633,7 +20630,7 @@
         <v>1</v>
       </c>
       <c r="R391" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S391" t="n">
         <v>0</v>
@@ -20686,7 +20683,7 @@
         <v>1</v>
       </c>
       <c r="R392" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S392" t="n">
         <v>0</v>
@@ -20739,7 +20736,7 @@
         <v>1</v>
       </c>
       <c r="R393" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S393" t="n">
         <v>0</v>
@@ -20792,7 +20789,7 @@
         <v>1</v>
       </c>
       <c r="R394" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S394" t="n">
         <v>0</v>
@@ -20845,7 +20842,7 @@
         <v>1</v>
       </c>
       <c r="R395" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S395" t="n">
         <v>0</v>
@@ -20898,7 +20895,7 @@
         <v>1</v>
       </c>
       <c r="R396" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S396" t="n">
         <v>0</v>
@@ -20951,7 +20948,7 @@
         <v>1</v>
       </c>
       <c r="R397" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S397" t="n">
         <v>0</v>
@@ -21000,7 +20997,7 @@
         <v>1</v>
       </c>
       <c r="R398" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S398" t="n">
         <v>0</v>
@@ -21053,7 +21050,7 @@
         <v>1</v>
       </c>
       <c r="R399" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S399" t="n">
         <v>0</v>
@@ -21106,7 +21103,7 @@
         <v>1</v>
       </c>
       <c r="R400" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S400" t="n">
         <v>0</v>
@@ -21159,7 +21156,7 @@
         <v>1</v>
       </c>
       <c r="R401" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S401" t="n">
         <v>0</v>
@@ -21212,7 +21209,7 @@
         <v>1</v>
       </c>
       <c r="R402" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S402" t="n">
         <v>0</v>
@@ -21265,7 +21262,7 @@
         <v>1</v>
       </c>
       <c r="R403" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S403" t="n">
         <v>0</v>
@@ -21318,7 +21315,7 @@
         <v>1</v>
       </c>
       <c r="R404" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S404" t="n">
         <v>0</v>
@@ -21357,7 +21354,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N405" t="inlineStr"/>
@@ -21368,10 +21365,10 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R405" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S405" t="n">
         <v>1</v>
@@ -21424,7 +21421,7 @@
         <v>0</v>
       </c>
       <c r="R406" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="S406" t="n">
         <v>1</v>
@@ -21463,7 +21460,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N407" t="inlineStr"/>
@@ -21477,7 +21474,7 @@
         <v>0</v>
       </c>
       <c r="R407" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S407" t="n">
         <v>1</v>
@@ -21512,7 +21509,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N408" t="inlineStr"/>
@@ -21522,7 +21519,7 @@
         <v>0</v>
       </c>
       <c r="R408" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S408" t="n">
         <v>1</v>
@@ -21567,7 +21564,7 @@
         <v>0</v>
       </c>
       <c r="R409" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S409" t="n">
         <v>0</v>
@@ -21612,7 +21609,7 @@
         <v>0</v>
       </c>
       <c r="R410" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S410" t="n">
         <v>1</v>
@@ -21657,7 +21654,7 @@
         <v>0</v>
       </c>
       <c r="R411" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S411" t="n">
         <v>0</v>
@@ -21702,7 +21699,7 @@
         <v>0</v>
       </c>
       <c r="R412" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S412" t="n">
         <v>0</v>
@@ -21716,7 +21713,7 @@
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>PT 약품</t>
+          <t>PT약품</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
@@ -21751,7 +21748,7 @@
         <v>0</v>
       </c>
       <c r="R413" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S413" t="n">
         <v>0</v>
@@ -21796,7 +21793,7 @@
         <v>0</v>
       </c>
       <c r="R414" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S414" t="n">
         <v>0</v>
@@ -21804,25 +21801,21 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B415" t="inlineStr"/>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream AA400-3⅓*17"</t>
         </is>
       </c>
       <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FILM</t>
         </is>
       </c>
       <c r="I415" t="inlineStr"/>
@@ -21845,7 +21838,7 @@
         <v>0</v>
       </c>
       <c r="R415" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S415" t="n">
         <v>0</v>
@@ -21853,24 +21846,28 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B416" t="inlineStr"/>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Carestream AA400-3⅓*17"</t>
+          <t>PT약품</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>현상제</t>
+        </is>
+      </c>
       <c r="G416" t="inlineStr"/>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>FILM</t>
-        </is>
-      </c>
-      <c r="I416" t="inlineStr"/>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>NAWOO</t>
+        </is>
+      </c>
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="n">
         <v>0</v>
@@ -21890,15 +21887,15 @@
         <v>0</v>
       </c>
       <c r="R416" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr"/>
@@ -21910,7 +21907,7 @@
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
-          <t>세척제</t>
+          <t>침투제</t>
         </is>
       </c>
       <c r="G417" t="inlineStr"/>
@@ -21939,7 +21936,7 @@
         <v>0</v>
       </c>
       <c r="R417" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S417" t="n">
         <v>1</v>
@@ -21947,7 +21944,7 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B418" t="inlineStr"/>
       <c r="C418" t="inlineStr"/>
@@ -21959,7 +21956,7 @@
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>침투제</t>
+          <t>세척제</t>
         </is>
       </c>
       <c r="G418" t="inlineStr"/>
@@ -21988,7 +21985,7 @@
         <v>0</v>
       </c>
       <c r="R418" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S418" t="n">
         <v>1</v>
@@ -21996,28 +21993,32 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B419" t="inlineStr"/>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>PT약품</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr"/>
+          <t>Carestream M100-14*17"</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>현상제</t>
-        </is>
-      </c>
-      <c r="G419" t="inlineStr"/>
+          <t>Carestream M100-14*17"</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
       <c r="H419" t="inlineStr"/>
-      <c r="I419" t="inlineStr">
-        <is>
-          <t>NAWOO</t>
-        </is>
-      </c>
+      <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="n">
         <v>0</v>
@@ -22037,15 +22038,15 @@
         <v>0</v>
       </c>
       <c r="R419" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S419" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B420" t="inlineStr"/>
       <c r="C420" t="inlineStr"/>
@@ -22090,7 +22091,7 @@
         <v>0</v>
       </c>
       <c r="R420" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S420" t="n">
         <v>0</v>
@@ -22098,7 +22099,7 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B421" t="inlineStr"/>
       <c r="C421" t="inlineStr"/>
@@ -22143,7 +22144,7 @@
         <v>0</v>
       </c>
       <c r="R421" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S421" t="n">
         <v>0</v>
@@ -22151,7 +22152,7 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B422" t="inlineStr"/>
       <c r="C422" t="inlineStr"/>
@@ -22196,7 +22197,7 @@
         <v>0</v>
       </c>
       <c r="R422" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S422" t="n">
         <v>0</v>
@@ -22204,7 +22205,7 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B423" t="inlineStr"/>
       <c r="C423" t="inlineStr"/>
@@ -22249,7 +22250,7 @@
         <v>0</v>
       </c>
       <c r="R423" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S423" t="n">
         <v>0</v>
@@ -22257,7 +22258,7 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B424" t="inlineStr"/>
       <c r="C424" t="inlineStr"/>
@@ -22292,7 +22293,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N424" t="inlineStr"/>
@@ -22302,21 +22303,21 @@
         <v>0</v>
       </c>
       <c r="R424" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Carestream M100-14*17"</t>
+          <t>Carestream MX125-10*12"</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -22326,7 +22327,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Carestream M100-14*17"</t>
+          <t>Carestream MX125-10*12"</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -22345,7 +22346,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N425" t="inlineStr"/>
@@ -22355,7 +22356,7 @@
         <v>0</v>
       </c>
       <c r="R425" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S425" t="n">
         <v>1</v>
@@ -22363,13 +22364,13 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B426" t="inlineStr"/>
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Carestream MX125-10*12"</t>
+          <t>PAUT SCANNER(MANUAL)</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -22379,7 +22380,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Carestream MX125-10*12"</t>
+          <t>PAUT SCANNER(MANUAL)</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -22408,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="R426" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S426" t="n">
         <v>1</v>
@@ -22416,7 +22417,7 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B427" t="inlineStr"/>
       <c r="C427" t="inlineStr"/>
@@ -22437,7 +22438,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>자동등록</t>
+          <t>수정등록</t>
         </is>
       </c>
       <c r="H427" t="inlineStr"/>
@@ -22461,15 +22462,15 @@
         <v>0</v>
       </c>
       <c r="R427" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S427" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B428" t="inlineStr"/>
       <c r="C428" t="inlineStr"/>
@@ -22514,7 +22515,7 @@
         <v>0</v>
       </c>
       <c r="R428" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S428" t="n">
         <v>0</v>
@@ -22522,13 +22523,13 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B429" t="inlineStr"/>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>PAUT SCANNER(MANUAL)</t>
+          <t>MT약품</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -22538,12 +22539,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>PAUT SCANNER(MANUAL)</t>
+          <t>백색페인트</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>수정등록</t>
+          <t>자동등록</t>
         </is>
       </c>
       <c r="H429" t="inlineStr"/>
@@ -22567,15 +22568,15 @@
         <v>0</v>
       </c>
       <c r="R429" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S429" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B430" t="inlineStr"/>
       <c r="C430" t="inlineStr"/>
@@ -22620,7 +22621,7 @@
         <v>0</v>
       </c>
       <c r="R430" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S430" t="n">
         <v>1</v>
@@ -22628,13 +22629,13 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B431" t="inlineStr"/>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>MT약품</t>
+          <t>432</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -22644,7 +22645,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>백색페인트</t>
+          <t>432</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -22673,27 +22674,31 @@
         <v>0</v>
       </c>
       <c r="R431" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S431" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B432" t="inlineStr"/>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>MT약품</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr"/>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>현장</t>
+          <t>432</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -22722,15 +22727,15 @@
         <v>0</v>
       </c>
       <c r="R432" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S432" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B433" t="inlineStr"/>
       <c r="C433" t="inlineStr"/>
@@ -22775,7 +22780,7 @@
         <v>0</v>
       </c>
       <c r="R433" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S433" t="n">
         <v>0</v>
@@ -22783,7 +22788,7 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B434" t="inlineStr"/>
       <c r="C434" t="inlineStr"/>
@@ -22828,7 +22833,7 @@
         <v>0</v>
       </c>
       <c r="R434" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S434" t="n">
         <v>0</v>
@@ -22836,13 +22841,13 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B435" t="inlineStr"/>
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>405</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -22852,7 +22857,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>405</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -22881,40 +22886,34 @@
         <v>0</v>
       </c>
       <c r="R435" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S435" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="n">
-        <v>438</v>
-      </c>
+      <c r="A436" t="inlineStr"/>
       <c r="B436" t="inlineStr"/>
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
-      <c r="H436" t="inlineStr"/>
-      <c r="I436" t="inlineStr"/>
+          <t>Carestream AA400-10*12"</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>FILM</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Carestream</t>
+        </is>
+      </c>
       <c r="J436" t="inlineStr"/>
       <c r="K436" t="n">
         <v>0</v>
@@ -22924,7 +22923,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N436" t="inlineStr"/>
@@ -22934,38 +22933,24 @@
         <v>0</v>
       </c>
       <c r="R436" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S436" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="n">
-        <v>439</v>
-      </c>
+      <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr"/>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
+          <t>Carestream M100-10*12"</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr"/>
       <c r="I437" t="inlineStr"/>
       <c r="J437" t="inlineStr"/>
@@ -22975,11 +22960,7 @@
       <c r="L437" t="n">
         <v>0</v>
       </c>
-      <c r="M437" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
+      <c r="M437" t="inlineStr"/>
       <c r="N437" t="inlineStr"/>
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
@@ -22987,7 +22968,7 @@
         <v>0</v>
       </c>
       <c r="R437" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S437" t="n">
         <v>0</v>
@@ -22999,22 +22980,14 @@
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Carestream AA400-10*12"</t>
+          <t>Carestream MX125-3⅓*6"</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr"/>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>FILM</t>
-        </is>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>Carestream</t>
-        </is>
-      </c>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="n">
         <v>0</v>
@@ -23022,11 +22995,7 @@
       <c r="L438" t="n">
         <v>0</v>
       </c>
-      <c r="M438" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
+      <c r="M438" t="inlineStr"/>
       <c r="N438" t="inlineStr"/>
       <c r="O438" t="inlineStr"/>
       <c r="P438" t="inlineStr"/>
@@ -23034,7 +23003,7 @@
         <v>0</v>
       </c>
       <c r="R438" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S438" t="n">
         <v>0</v>
@@ -23046,7 +23015,7 @@
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Carestream M100-10*12"</t>
+          <t>Carestream MX125-4½*12"</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -23069,7 +23038,7 @@
         <v>0</v>
       </c>
       <c r="R439" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S439" t="n">
         <v>0</v>
@@ -23081,7 +23050,7 @@
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Carestream MX125-3⅓*6"</t>
+          <t>Carestream MX125-14*17"</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -23104,7 +23073,7 @@
         <v>0</v>
       </c>
       <c r="R440" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S440" t="n">
         <v>0</v>
@@ -23116,7 +23085,7 @@
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Carestream MX125-4½*12"</t>
+          <t>Carestream T200-4½*12"</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -23139,7 +23108,7 @@
         <v>0</v>
       </c>
       <c r="R441" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S441" t="n">
         <v>0</v>
@@ -23151,7 +23120,7 @@
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Carestream MX125-14*17"</t>
+          <t>Carestream T200-14*17"</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -23174,23 +23143,29 @@
         <v>0</v>
       </c>
       <c r="R442" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S442" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr"/>
+      <c r="A443" t="n">
+        <v>442</v>
+      </c>
       <c r="B443" t="inlineStr"/>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Carestream T200-4½*12"</t>
+          <t>MT약품</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr"/>
@@ -23201,7 +23176,11 @@
       <c r="L443" t="n">
         <v>0</v>
       </c>
-      <c r="M443" t="inlineStr"/>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
       <c r="N443" t="inlineStr"/>
       <c r="O443" t="inlineStr"/>
       <c r="P443" t="inlineStr"/>
@@ -23209,19 +23188,21 @@
         <v>0</v>
       </c>
       <c r="R443" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S443" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr"/>
+      <c r="A444" t="n">
+        <v>444</v>
+      </c>
       <c r="B444" t="inlineStr"/>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Carestream T200-14*17"</t>
+          <t>PAUT SCANNER(MANUAL)</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
@@ -23236,7 +23217,11 @@
       <c r="L444" t="n">
         <v>0</v>
       </c>
-      <c r="M444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
       <c r="N444" t="inlineStr"/>
       <c r="O444" t="inlineStr"/>
       <c r="P444" t="inlineStr"/>
@@ -23244,7 +23229,7 @@
         <v>0</v>
       </c>
       <c r="R444" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S444" t="n">
         <v>0</v>
@@ -23252,28 +23237,24 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B445" t="inlineStr"/>
       <c r="C445" t="inlineStr"/>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>MT약품</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>백색페인트</t>
-        </is>
-      </c>
-      <c r="G445" t="inlineStr"/>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
       <c r="H445" t="inlineStr"/>
-      <c r="I445" t="inlineStr">
-        <is>
-          <t>NAWOO</t>
-        </is>
-      </c>
+      <c r="I445" t="inlineStr"/>
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="n">
         <v>0</v>
@@ -23283,7 +23264,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="N445" t="inlineStr"/>
@@ -23293,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="R445" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S445" t="n">
         <v>1</v>
@@ -23301,7 +23282,7 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B446" t="inlineStr"/>
       <c r="C446" t="inlineStr"/>
@@ -23310,19 +23291,23 @@
           <t>PT약품</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr"/>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>세척제</t>
-        </is>
-      </c>
-      <c r="G446" t="inlineStr"/>
+          <t>PT약품</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>수정등록</t>
+        </is>
+      </c>
       <c r="H446" t="inlineStr"/>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>NAWOO</t>
-        </is>
-      </c>
+      <c r="I446" t="inlineStr"/>
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="n">
         <v>0</v>
@@ -23332,7 +23317,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="N446" t="inlineStr"/>
@@ -23342,7 +23327,7 @@
         <v>0</v>
       </c>
       <c r="R446" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S446" t="n">
         <v>0</v>
@@ -23350,19 +23335,19 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="B447" t="inlineStr"/>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
         <is>
-          <t>MT약품</t>
+          <t>PAUT 장비</t>
         </is>
       </c>
       <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MX2</t>
         </is>
       </c>
       <c r="G447" t="inlineStr"/>
@@ -23387,7 +23372,7 @@
         <v>0</v>
       </c>
       <c r="R447" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S447" t="n">
         <v>0</v>
@@ -23395,19 +23380,19 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B448" t="inlineStr"/>
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>PAUT장비</t>
         </is>
       </c>
       <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MX2</t>
         </is>
       </c>
       <c r="G448" t="inlineStr"/>
@@ -23432,26 +23417,38 @@
         <v>0</v>
       </c>
       <c r="R448" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B449" t="inlineStr"/>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
-          <t>PAUT SCANNER(MANUAL)</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
+          <t>Carestream AA400-10*12"</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>현장</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Carestream AA400-10*12"</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>자동등록</t>
+        </is>
+      </c>
       <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr"/>
@@ -23463,7 +23460,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N449" t="inlineStr"/>
@@ -23473,25 +23470,33 @@
         <v>0</v>
       </c>
       <c r="R449" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B450" t="inlineStr"/>
       <c r="C450" t="inlineStr"/>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Carestream T200-4½*12"</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>현장</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Carestream T200-4½*12"</t>
+        </is>
+      </c>
       <c r="G450" t="inlineStr">
         <is>
           <t>자동등록</t>
@@ -23508,7 +23513,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N450" t="inlineStr"/>
@@ -23526,13 +23531,13 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B451" t="inlineStr"/>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream MX125-10*12"</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -23542,12 +23547,12 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream MX125-10*12"</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>수정등록</t>
+          <t>자동등록</t>
         </is>
       </c>
       <c r="H451" t="inlineStr"/>
@@ -23561,7 +23566,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N451" t="inlineStr"/>
@@ -23579,13 +23584,13 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B452" t="inlineStr"/>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream MX125-3⅓*6"</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -23595,7 +23600,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream MX125-3⅓*6"</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -23614,7 +23619,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N452" t="inlineStr"/>
@@ -23632,13 +23637,13 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="B453" t="inlineStr"/>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream M100-10*12"</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -23648,7 +23653,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream M100-10*12"</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
@@ -23667,7 +23672,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N453" t="inlineStr"/>
@@ -23685,13 +23690,13 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B454" t="inlineStr"/>
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream MX125-10*12"</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -23701,12 +23706,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream MX125-10*12"</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>수정등록</t>
+          <t>자동등록</t>
         </is>
       </c>
       <c r="H454" t="inlineStr"/>
@@ -23720,7 +23725,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>매</t>
         </is>
       </c>
       <c r="N454" t="inlineStr"/>
@@ -23738,13 +23743,13 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B455" t="inlineStr"/>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream MX125-10*12"</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -23754,7 +23759,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>PT약품</t>
+          <t>Carestream MX125-10*12"</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
@@ -23786,520 +23791,6 @@
         <v>10</v>
       </c>
       <c r="S455" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="n">
-        <v>453</v>
-      </c>
-      <c r="B456" t="inlineStr"/>
-      <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>PAUT 장비</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>MX2</t>
-        </is>
-      </c>
-      <c r="G456" t="inlineStr"/>
-      <c r="H456" t="inlineStr"/>
-      <c r="I456" t="inlineStr"/>
-      <c r="J456" t="inlineStr"/>
-      <c r="K456" t="n">
-        <v>0</v>
-      </c>
-      <c r="L456" t="n">
-        <v>0</v>
-      </c>
-      <c r="M456" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="N456" t="inlineStr"/>
-      <c r="O456" t="inlineStr"/>
-      <c r="P456" t="inlineStr"/>
-      <c r="Q456" t="n">
-        <v>0</v>
-      </c>
-      <c r="R456" t="n">
-        <v>0</v>
-      </c>
-      <c r="S456" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="n">
-        <v>454</v>
-      </c>
-      <c r="B457" t="inlineStr"/>
-      <c r="C457" t="inlineStr"/>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>PAUT장비</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr">
-        <is>
-          <t>MX2</t>
-        </is>
-      </c>
-      <c r="G457" t="inlineStr"/>
-      <c r="H457" t="inlineStr"/>
-      <c r="I457" t="inlineStr"/>
-      <c r="J457" t="inlineStr"/>
-      <c r="K457" t="n">
-        <v>0</v>
-      </c>
-      <c r="L457" t="n">
-        <v>0</v>
-      </c>
-      <c r="M457" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="N457" t="inlineStr"/>
-      <c r="O457" t="inlineStr"/>
-      <c r="P457" t="inlineStr"/>
-      <c r="Q457" t="n">
-        <v>0</v>
-      </c>
-      <c r="R457" t="n">
-        <v>0</v>
-      </c>
-      <c r="S457" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="n">
-        <v>455</v>
-      </c>
-      <c r="B458" t="inlineStr"/>
-      <c r="C458" t="inlineStr"/>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>PT약품</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F458" t="inlineStr">
-        <is>
-          <t>PT약품</t>
-        </is>
-      </c>
-      <c r="G458" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
-      <c r="H458" t="inlineStr"/>
-      <c r="I458" t="inlineStr"/>
-      <c r="J458" t="inlineStr"/>
-      <c r="K458" t="n">
-        <v>0</v>
-      </c>
-      <c r="L458" t="n">
-        <v>0</v>
-      </c>
-      <c r="M458" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="N458" t="inlineStr"/>
-      <c r="O458" t="inlineStr"/>
-      <c r="P458" t="inlineStr"/>
-      <c r="Q458" t="n">
-        <v>0</v>
-      </c>
-      <c r="R458" t="n">
-        <v>10</v>
-      </c>
-      <c r="S458" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="n">
-        <v>456</v>
-      </c>
-      <c r="B459" t="inlineStr"/>
-      <c r="C459" t="inlineStr"/>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>Carestream AA400-10*12"</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>Carestream AA400-10*12"</t>
-        </is>
-      </c>
-      <c r="G459" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
-      <c r="H459" t="inlineStr"/>
-      <c r="I459" t="inlineStr"/>
-      <c r="J459" t="inlineStr"/>
-      <c r="K459" t="n">
-        <v>0</v>
-      </c>
-      <c r="L459" t="n">
-        <v>0</v>
-      </c>
-      <c r="M459" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="N459" t="inlineStr"/>
-      <c r="O459" t="inlineStr"/>
-      <c r="P459" t="inlineStr"/>
-      <c r="Q459" t="n">
-        <v>0</v>
-      </c>
-      <c r="R459" t="n">
-        <v>10</v>
-      </c>
-      <c r="S459" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="n">
-        <v>457</v>
-      </c>
-      <c r="B460" t="inlineStr"/>
-      <c r="C460" t="inlineStr"/>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>Carestream T200-4½*12"</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F460" t="inlineStr">
-        <is>
-          <t>Carestream T200-4½*12"</t>
-        </is>
-      </c>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
-      <c r="H460" t="inlineStr"/>
-      <c r="I460" t="inlineStr"/>
-      <c r="J460" t="inlineStr"/>
-      <c r="K460" t="n">
-        <v>0</v>
-      </c>
-      <c r="L460" t="n">
-        <v>0</v>
-      </c>
-      <c r="M460" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="N460" t="inlineStr"/>
-      <c r="O460" t="inlineStr"/>
-      <c r="P460" t="inlineStr"/>
-      <c r="Q460" t="n">
-        <v>0</v>
-      </c>
-      <c r="R460" t="n">
-        <v>10</v>
-      </c>
-      <c r="S460" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="n">
-        <v>458</v>
-      </c>
-      <c r="B461" t="inlineStr"/>
-      <c r="C461" t="inlineStr"/>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>Carestream MX125-10*12"</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F461" t="inlineStr">
-        <is>
-          <t>Carestream MX125-10*12"</t>
-        </is>
-      </c>
-      <c r="G461" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
-      <c r="H461" t="inlineStr"/>
-      <c r="I461" t="inlineStr"/>
-      <c r="J461" t="inlineStr"/>
-      <c r="K461" t="n">
-        <v>0</v>
-      </c>
-      <c r="L461" t="n">
-        <v>0</v>
-      </c>
-      <c r="M461" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="N461" t="inlineStr"/>
-      <c r="O461" t="inlineStr"/>
-      <c r="P461" t="inlineStr"/>
-      <c r="Q461" t="n">
-        <v>0</v>
-      </c>
-      <c r="R461" t="n">
-        <v>10</v>
-      </c>
-      <c r="S461" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="n">
-        <v>459</v>
-      </c>
-      <c r="B462" t="inlineStr"/>
-      <c r="C462" t="inlineStr"/>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>Carestream MX125-3⅓*6"</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>Carestream MX125-3⅓*6"</t>
-        </is>
-      </c>
-      <c r="G462" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
-      <c r="H462" t="inlineStr"/>
-      <c r="I462" t="inlineStr"/>
-      <c r="J462" t="inlineStr"/>
-      <c r="K462" t="n">
-        <v>0</v>
-      </c>
-      <c r="L462" t="n">
-        <v>0</v>
-      </c>
-      <c r="M462" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="N462" t="inlineStr"/>
-      <c r="O462" t="inlineStr"/>
-      <c r="P462" t="inlineStr"/>
-      <c r="Q462" t="n">
-        <v>0</v>
-      </c>
-      <c r="R462" t="n">
-        <v>10</v>
-      </c>
-      <c r="S462" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="n">
-        <v>460</v>
-      </c>
-      <c r="B463" t="inlineStr"/>
-      <c r="C463" t="inlineStr"/>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>Carestream M100-10*12"</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F463" t="inlineStr">
-        <is>
-          <t>Carestream M100-10*12"</t>
-        </is>
-      </c>
-      <c r="G463" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
-      <c r="H463" t="inlineStr"/>
-      <c r="I463" t="inlineStr"/>
-      <c r="J463" t="inlineStr"/>
-      <c r="K463" t="n">
-        <v>0</v>
-      </c>
-      <c r="L463" t="n">
-        <v>0</v>
-      </c>
-      <c r="M463" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="N463" t="inlineStr"/>
-      <c r="O463" t="inlineStr"/>
-      <c r="P463" t="inlineStr"/>
-      <c r="Q463" t="n">
-        <v>0</v>
-      </c>
-      <c r="R463" t="n">
-        <v>10</v>
-      </c>
-      <c r="S463" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="n">
-        <v>461</v>
-      </c>
-      <c r="B464" t="inlineStr"/>
-      <c r="C464" t="inlineStr"/>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>Carestream MX125-10*12"</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F464" t="inlineStr">
-        <is>
-          <t>Carestream MX125-10*12"</t>
-        </is>
-      </c>
-      <c r="G464" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
-      <c r="H464" t="inlineStr"/>
-      <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
-      <c r="K464" t="n">
-        <v>0</v>
-      </c>
-      <c r="L464" t="n">
-        <v>0</v>
-      </c>
-      <c r="M464" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="N464" t="inlineStr"/>
-      <c r="O464" t="inlineStr"/>
-      <c r="P464" t="inlineStr"/>
-      <c r="Q464" t="n">
-        <v>0</v>
-      </c>
-      <c r="R464" t="n">
-        <v>10</v>
-      </c>
-      <c r="S464" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="n">
-        <v>462</v>
-      </c>
-      <c r="B465" t="inlineStr"/>
-      <c r="C465" t="inlineStr"/>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>MT약품</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr">
-        <is>
-          <t>현장</t>
-        </is>
-      </c>
-      <c r="F465" t="inlineStr">
-        <is>
-          <t>MT약품</t>
-        </is>
-      </c>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>자동등록</t>
-        </is>
-      </c>
-      <c r="H465" t="inlineStr"/>
-      <c r="I465" t="inlineStr"/>
-      <c r="J465" t="inlineStr"/>
-      <c r="K465" t="n">
-        <v>0</v>
-      </c>
-      <c r="L465" t="n">
-        <v>0</v>
-      </c>
-      <c r="M465" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="N465" t="inlineStr"/>
-      <c r="O465" t="inlineStr"/>
-      <c r="P465" t="inlineStr"/>
-      <c r="Q465" t="n">
-        <v>0</v>
-      </c>
-      <c r="R465" t="n">
-        <v>10</v>
-      </c>
-      <c r="S465" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24314,7 +23805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24436,10 +23927,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45778</v>
+        <v>46149</v>
       </c>
       <c r="B2" t="n">
-        <v>410</v>
+        <v>462</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -24466,17 +23957,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>스타렉스91주8839</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -24496,273 +23987,6 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B3" t="n">
-        <v>405</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-100</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>K1-PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B4" t="n">
-        <v>408</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>-100</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>K1-PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>45778.88671622195</v>
-      </c>
-      <c r="B5" t="n">
-        <v>433</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>K1-PJT 현장 사용 (자동 차감) (nan)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>45778.88671622195</v>
-      </c>
-      <c r="B6" t="n">
-        <v>434</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>K1-PJT 현장 사용 (자동 차감) (nan)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B7" t="n">
-        <v>462</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>-20</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>K1-PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24836,7 +24060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25243,7 +24467,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45778</v>
+        <v>46149</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -25251,20 +24475,20 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>410</v>
+        <v>462</v>
       </c>
       <c r="D2" t="n">
         <v>100</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="1" t="n">
-        <v>46147.34000990741</v>
+        <v>46149.60385072917</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -25288,7 +24512,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R-RAY(Se-75)</t>
+          <t>R-RAY</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -25316,59 +24540,41 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>(주야간) 09:00~24:00</t>
+          <t>(주간) 09:00~21:00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
@@ -25390,25 +24596,13 @@
       <c r="BF2" t="n">
         <v>0</v>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr">
@@ -25444,622 +24638,6 @@
       <c r="CB2" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>405</v>
-      </c>
-      <c r="D3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="1" t="n">
-        <v>46147.87794667824</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>408</v>
-      </c>
-      <c r="D4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="1" t="n">
-        <v>46147.87911841435</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25500</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2550000</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>K1-PJT</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>462</v>
-      </c>
-      <c r="D5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>46147.88671621533</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4300</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>86000</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>스타렉스91주8839</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>out_exterior:양호|out_cleanliness:양호|out_cleaning:함|out_locking:잠금|in_exterior:양호|in_cleanliness:양호|in_cleaning:함|in_locking:잠금</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>롯데건설</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -1,18 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="DailyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Budget" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21717,11 +21715,7 @@
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
@@ -23161,11 +23155,7 @@
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr"/>
@@ -23955,26 +23945,10 @@
           <t>K1-PJT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -23994,67 +23968,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Material ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Entry Date</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>MaterialID</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>EntryDate</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24644,630 +24557,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Site</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>LaborCost</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>MaterialCost</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>OutsourceCost</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Profit</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>LaborDetail</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>MaterialDetail</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ExpenseDetail</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>UnitPrice</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Spec</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>이사</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>55250000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>부장</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>55250000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>차장</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>47670000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>과장</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>41170000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>대리</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>37920000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>계장</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>34670000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>주임</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
-        <v>31420000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Labor</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>기사</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
-        <v>29250000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PT 약품</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>세척액</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PT 약품</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>침투액</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PT 약품</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>현상액</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MT 약품</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>자분페인트</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>2350</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MT 약품</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>흑색자분</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>방사선투과검사 필름</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MX125</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>글리세린</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>20L</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>통</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>필름 현상액</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3L</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>통</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>16500</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>필름 정착액</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3L</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>통</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>16500</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>수적방지액</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>200mL</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>통</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>차량유지비</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>주유, 수리, 통행, 주차 등</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>소모품비</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>장갑,일회용 작업복외</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>복리후생비</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>생수, 음료 외 기타</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1666</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Se-175</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>방사성동위원소 구매</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>35714</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Outsource</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>케이엔디이</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>방사선투과검사</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>공수</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DailyUsage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Budget" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonthlyUsage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DailyUsage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21715,7 +21717,11 @@
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
@@ -23155,7 +23161,11 @@
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr"/>
@@ -23945,10 +23955,26 @@
           <t>K1-PJT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -23968,6 +23994,57 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MaterialID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>EntryDate</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24557,15 +24634,590 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>UnitPrice</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>LaborDetail</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MaterialDetail</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ExpenseDetail</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>이사</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>55250000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>부장</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>55250000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차장</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>47670000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>과장</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>41170000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대리</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>37920000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>계장</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>34670000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>주임</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>31420000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>기사</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>29250000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PT 약품</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>세척제</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PT 약품</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>침투제</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PT 약품</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>현상제</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MT 약품</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>백색페인트</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MT 약품</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>흑색자분</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>방사선투과검사 필름</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MX125</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>글리세린</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20L</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>통</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>필름 현상액</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3L</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>통</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>필름 정착액</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3L</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>통</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>수적방지액</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>200mL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>통</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>차량유지비</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>주유, 수리, 통행, 주차 등</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>소모품비</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>장갑,일회용 작업복외</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>복리후생비</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>생수, 음료 외 기타</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Se-175</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>방사성동위원소 구매</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>35714</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Outsource</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>케이엔디이</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>방사선투과검사</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>공수</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -23277,7 +23277,7 @@
         <v>10</v>
       </c>
       <c r="S445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446">

--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -21567,7 +21567,7 @@
         <v>10</v>
       </c>
       <c r="S409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -23927,10 +23927,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46149</v>
+        <v>46185</v>
       </c>
       <c r="B2" t="n">
-        <v>462</v>
+        <v>409</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -23938,21 +23938,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>K1-PJT 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
+          <t>의왕 주배관 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>K1-PJT</t>
+          <t>의왕 주배관</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -24050,7 +24046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24451,28 +24447,83 @@
       </c>
       <c r="CB1" t="inlineStr">
         <is>
+          <t>작업형태</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>조건1</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>조건2</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>제경비율</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>기술료율</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>보정계수</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>환산물량</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>재료비</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>인건비</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>제경비</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>기술료</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
           <t>수량</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46149</v>
+        <v>46185</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>K1-PJT</t>
+          <t>의왕 주배관</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>462</v>
+        <v>409</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="1" t="n">
-        <v>46149.60385072917</v>
+        <v>46190.97575810185</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -24495,21 +24546,17 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>부장 주진철</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>R-RAY</t>
+          <t>R-RAY(Se-75)</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>25500</v>
+        <v>69810</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -24518,7 +24565,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2550000</v>
+        <v>1745243</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -24528,16 +24575,8 @@
       <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>(주간) 09:00~21:00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -24597,7 +24636,7 @@
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>롯데건설</t>
+          <t>가스공사</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr"/>
@@ -24607,16 +24646,8 @@
       <c r="BS2" t="inlineStr"/>
       <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>ASME B31.3</t>
-        </is>
-      </c>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="inlineStr">
@@ -24625,7 +24656,42 @@
         </is>
       </c>
       <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="n">
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>Ir-192 또는 Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>15mm 이하 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>25</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>84475</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>871575</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>697260</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>91933</v>
+      </c>
+      <c r="CM2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -21371,7 +21371,7 @@
         <v>10</v>
       </c>
       <c r="S405" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -21477,7 +21477,7 @@
         <v>10</v>
       </c>
       <c r="S407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -21522,7 +21522,7 @@
         <v>10</v>
       </c>
       <c r="S408" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -21612,7 +21612,7 @@
         <v>10</v>
       </c>
       <c r="S410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -22306,7 +22306,7 @@
         <v>10</v>
       </c>
       <c r="S424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425">
@@ -22359,7 +22359,7 @@
         <v>10</v>
       </c>
       <c r="S425" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
@@ -22571,7 +22571,7 @@
         <v>10</v>
       </c>
       <c r="S429" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -22624,7 +22624,7 @@
         <v>10</v>
       </c>
       <c r="S430" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431">
@@ -23473,7 +23473,7 @@
         <v>10</v>
       </c>
       <c r="S449" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450">
@@ -23632,7 +23632,7 @@
         <v>10</v>
       </c>
       <c r="S452" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -23685,7 +23685,7 @@
         <v>10</v>
       </c>
       <c r="S453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -23791,7 +23791,7 @@
         <v>10</v>
       </c>
       <c r="S455" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -21,10 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -54,9 +51,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -23805,7 +23801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23924,65 +23920,6 @@
           <t>수량</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="B2" t="n">
-        <v>409</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>-25</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>의왕 주배관 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>의왕 주배관</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24046,7 +23983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM2"/>
+  <dimension ref="A1:CL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24499,200 +24436,6 @@
         <is>
           <t>기술료</t>
         </is>
-      </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46185</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>의왕 주배관</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>409</v>
-      </c>
-      <c r="D2" t="n">
-        <v>25</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="1" t="n">
-        <v>46190.97575810185</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>69810</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1745243</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>가스공사</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>Ir-192 또는 Se-75 (1.0)</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>15mm 이하 (1.0)</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr"/>
-      <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>25</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>84475</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>871575</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>697260</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>91933</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -21,9 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,9 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -23927,7 +23930,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46185</v>
+        <v>46198</v>
       </c>
       <c r="B2" t="n">
         <v>409</v>
@@ -23942,35 +23945,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>의왕 주배관 현장 사용 (자동 차감)</t>
+          <t>가산~가평 현장 사용 (자동 차감)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>의왕 주배관</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+          <t>가산~가평</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -24046,7 +24033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM2"/>
+  <dimension ref="A1:CL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24500,19 +24487,14 @@
           <t>기술료</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46185</v>
+      <c r="A2" s="2" t="n">
+        <v>46198</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>의왕 주배관</t>
+          <t>가산~가평</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -24523,7 +24505,7 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="1" t="n">
-        <v>46190.97575810185</v>
+        <v>46198.00841747563</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -24556,7 +24538,7 @@
         <v>25</v>
       </c>
       <c r="Q2" t="n">
-        <v>69810</v>
+        <v>132359</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -24565,7 +24547,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1745243</v>
+        <v>3308975</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -24646,7 +24628,11 @@
       <c r="BS2" t="inlineStr"/>
       <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>Pipe</t>
+        </is>
+      </c>
       <c r="BW2" t="inlineStr"/>
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
@@ -24658,7 +24644,7 @@
       <c r="CA2" t="inlineStr"/>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>야간</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -24683,16 +24669,13 @@
         <v>84475</v>
       </c>
       <c r="CJ2" t="n">
-        <v>871575</v>
+        <v>1692225</v>
       </c>
       <c r="CK2" t="n">
-        <v>697260</v>
+        <v>1353780</v>
       </c>
       <c r="CL2" t="n">
-        <v>91933</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>0</v>
+        <v>178495</v>
       </c>
     </row>
   </sheetData>

--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -21,11 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -56,10 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21615,7 +21612,7 @@
         <v>10</v>
       </c>
       <c r="S410" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
@@ -23941,7 +23938,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-25</v>
+        <v>-1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -23954,10 +23951,26 @@
           <t>가산~가평</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -24033,7 +24046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL2"/>
+  <dimension ref="A1:CM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24487,9 +24500,14 @@
           <t>기술료</t>
         </is>
       </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46198</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -24501,11 +24519,11 @@
         <v>409</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="1" t="n">
-        <v>46198.00841747563</v>
+        <v>46198.41365496528</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -24535,10 +24553,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>132359</v>
+        <v>125062</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -24547,7 +24565,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3308975</v>
+        <v>125062</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -24630,10 +24648,14 @@
       <c r="BU2" t="inlineStr"/>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>Pipe</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr"/>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>KS B 0845</t>
+        </is>
+      </c>
       <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="inlineStr">
@@ -24663,19 +24685,22 @@
         <v>1</v>
       </c>
       <c r="CH2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="CI2" t="n">
-        <v>84475</v>
+        <v>3379</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1692225</v>
+        <v>63860</v>
       </c>
       <c r="CK2" t="n">
-        <v>1353780</v>
+        <v>51088</v>
       </c>
       <c r="CL2" t="n">
-        <v>178495</v>
+        <v>6735</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -21,10 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -54,9 +51,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -23805,7 +23801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23924,65 +23920,6 @@
           <t>수량</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="B2" t="n">
-        <v>409</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>가산~가평 현장 사용 (자동 차감)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>가산~가평</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24046,7 +23983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM2"/>
+  <dimension ref="A1:CM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24504,203 +24441,6 @@
         <is>
           <t>수량</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>가산~가평</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>409</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="1" t="n">
-        <v>46198.41365496528</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>R-RAY(Se-75)</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>125062</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>125062</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>RT</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>가스공사</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>PIPE</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>KS B 0845</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>매</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>야간</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>Ir-192 또는 Se-75 (1.0)</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>15mm 이하 (1.0)</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr"/>
-      <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>3379</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>63860</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>51088</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>6735</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Na-aba/home/data/Material_Inventory.xlsx
+++ b/Na-aba/home/data/Material_Inventory.xlsx
@@ -21,7 +21,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -51,8 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -23801,7 +23808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23920,6 +23927,53 @@
           <t>수량</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B2" t="n">
+        <v>409</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-40</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>가산~가평 현장 사용 (자동 차감)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>부장 주진철, 부장 박광복, 주임 김성렬</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>가산~가평</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23983,7 +24037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM1"/>
+  <dimension ref="A1:CL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24437,10 +24491,235 @@
           <t>기술료</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>가산~가평</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>409</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="1" t="n">
+        <v>46200.50579772082</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>부장 주진철</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>R-RAY(Se-75)</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>124865</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4994591</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>(휴일) 09:00~19:00</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>75,000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>부장 박광복</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>(휴일) 09:00~19:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>75,000</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>주임 김성렬</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>(휴일) 09:00~19:00</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>75,000</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>가스공사</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>PIPE</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>KS B 0845</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>매</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>휴일</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>Ir-192 또는 Se-75 (1.0)</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>15mm 이하 (1.0)</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>40</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>135160</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>2550240</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>2040192</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>268999</v>
       </c>
     </row>
   </sheetData>
